--- a/Data/Export/Common/Technique_技术.xlsx
+++ b/Data/Export/Common/Technique_技术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CF09F1-99A5-4D41-BE94-048B11078899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC86D772-04A6-4959-AE39-9957EDA2266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5385" yWindow="2685" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Techniques" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="192">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -355,10 +355,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ai32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>说明</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -387,10 +383,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>needTechs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>效果集</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -479,10 +471,6 @@
   </si>
   <si>
     <t>[{class:"CityDurabilityLimit", value:3000, kinds:[1,2,3]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[class:"BuildingBaseAttackBack", value:"200"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -685,6 +673,70 @@
   </si>
   <si>
     <t>[{class:"ForceTroopMaxTroop", value:3000}]</t>
+  </si>
+  <si>
+    <t>[{class:"BuildingBaseAttackBack", value:"200"}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>needTech</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>测试5</t>
+  </si>
+  <si>
+    <t>测试6</t>
+  </si>
+  <si>
+    <t>测试7</t>
+  </si>
+  <si>
+    <t>测试8</t>
   </si>
 </sst>
 </file>
@@ -808,7 +860,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -824,9 +876,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1192,7 +1241,7 @@
     <col min="10" max="10" width="14.25" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.75" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" style="2" customWidth="1"/>
     <col min="14" max="14" width="10.5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.75" style="2" bestFit="1" customWidth="1"/>
@@ -1201,60 +1250,60 @@
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="12"/>
-      <c r="B1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="14" t="s">
+    <row r="1" spans="1:25" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="11"/>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="13"/>
+      <c r="F1" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M1" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="13"/>
+      <c r="Q1" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="7"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="6"/>
     </row>
     <row r="2" spans="1:25" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -1275,7 +1324,7 @@
       <c r="N2"/>
       <c r="O2"/>
       <c r="P2"/>
-      <c r="Q2" s="20"/>
+      <c r="Q2" s="19"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -1288,116 +1337,116 @@
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="H3" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="M3" s="8" t="s">
+      <c r="L3" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8" t="s">
+      <c r="O3" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="R3" s="16"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-    </row>
-    <row r="4" spans="1:25" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R3" s="15"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="F4" s="11" t="s">
+      <c r="C4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="K4" s="11" t="s">
+      <c r="H4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="M4" s="11" t="s">
+      <c r="L4" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="O4" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="P4" s="15" t="s">
+      <c r="O4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="P4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="R4" s="18" t="s">
+      <c r="Q4" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -1428,7 +1477,7 @@
         <v>1000</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M5" s="4">
         <v>2000</v>
@@ -1439,10 +1488,10 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>129</v>
+        <v>164</v>
+      </c>
+      <c r="R5" s="16" t="s">
+        <v>126</v>
       </c>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
@@ -1451,7 +1500,7 @@
     </row>
     <row r="6" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1482,7 +1531,7 @@
         <v>2000</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M6" s="4">
         <v>3000</v>
@@ -1496,8 +1545,8 @@
       <c r="P6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="R6" s="17" t="s">
-        <v>130</v>
+      <c r="R6" s="16" t="s">
+        <v>127</v>
       </c>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
@@ -1505,7 +1554,7 @@
       <c r="X6" s="4"/>
     </row>
     <row r="7" spans="1:25" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -1536,7 +1585,7 @@
         <v>3000</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M7" s="4">
         <v>5000</v>
@@ -1550,8 +1599,8 @@
       <c r="P7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="17" t="s">
-        <v>131</v>
+      <c r="R7" s="16" t="s">
+        <v>128</v>
       </c>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
@@ -1559,11 +1608,11 @@
       <c r="X7" s="4"/>
     </row>
     <row r="8" spans="1:25" ht="27" x14ac:dyDescent="0.15">
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>15</v>
@@ -1590,7 +1639,7 @@
         <v>5000</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M8" s="4">
         <v>8000</v>
@@ -1605,10 +1654,10 @@
         <v>13</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="R8" s="17" t="s">
-        <v>132</v>
+        <v>166</v>
+      </c>
+      <c r="R8" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -1616,7 +1665,7 @@
       <c r="X8" s="4"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -1647,7 +1696,7 @@
         <v>1000</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M9" s="4">
         <v>2000</v>
@@ -1658,10 +1707,10 @@
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R9" s="17" t="s">
-        <v>133</v>
+        <v>165</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>130</v>
       </c>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
@@ -1669,7 +1718,7 @@
       <c r="X9" s="4"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1700,7 +1749,7 @@
         <v>2000</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M10" s="4">
         <v>3000</v>
@@ -1714,8 +1763,8 @@
       <c r="P10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R10" s="17" t="s">
-        <v>134</v>
+      <c r="R10" s="16" t="s">
+        <v>131</v>
       </c>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
@@ -1723,7 +1772,7 @@
       <c r="X10" s="4"/>
     </row>
     <row r="11" spans="1:25" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="B11" s="4">
+      <c r="B11" s="2">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1754,7 +1803,7 @@
         <v>3000</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M11" s="4">
         <v>5000</v>
@@ -1768,8 +1817,8 @@
       <c r="P11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="R11" s="17" t="s">
-        <v>135</v>
+      <c r="R11" s="16" t="s">
+        <v>132</v>
       </c>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
@@ -1777,7 +1826,7 @@
       <c r="X11" s="4"/>
     </row>
     <row r="12" spans="1:25" ht="27" x14ac:dyDescent="0.15">
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>8</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1808,7 +1857,7 @@
         <v>5000</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M12" s="4">
         <v>8000</v>
@@ -1823,10 +1872,10 @@
         <v>21</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="R12" s="17" t="s">
-        <v>136</v>
+        <v>167</v>
+      </c>
+      <c r="R12" s="16" t="s">
+        <v>133</v>
       </c>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
@@ -1834,7 +1883,7 @@
       <c r="X12" s="4"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -1865,7 +1914,7 @@
         <v>1000</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M13" s="4">
         <v>2000</v>
@@ -1876,10 +1925,10 @@
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>137</v>
+        <v>168</v>
+      </c>
+      <c r="R13" s="16" t="s">
+        <v>134</v>
       </c>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -1887,7 +1936,7 @@
       <c r="X13" s="4"/>
     </row>
     <row r="14" spans="1:25" ht="54" x14ac:dyDescent="0.15">
-      <c r="B14" s="4">
+      <c r="B14" s="2">
         <v>10</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -1918,7 +1967,7 @@
         <v>2000</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M14" s="4">
         <v>3000</v>
@@ -1932,8 +1981,8 @@
       <c r="P14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="R14" s="17" t="s">
-        <v>138</v>
+      <c r="R14" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -1941,7 +1990,7 @@
       <c r="X14" s="4"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="B15" s="4">
+      <c r="B15" s="2">
         <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -1972,7 +2021,7 @@
         <v>3000</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M15" s="4">
         <v>5000</v>
@@ -1986,8 +2035,8 @@
       <c r="P15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="17" t="s">
-        <v>139</v>
+      <c r="R15" s="16" t="s">
+        <v>136</v>
       </c>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
@@ -1995,7 +2044,7 @@
       <c r="X15" s="4"/>
     </row>
     <row r="16" spans="1:25" ht="27" x14ac:dyDescent="0.15">
-      <c r="B16" s="4">
+      <c r="B16" s="2">
         <v>12</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2026,7 +2075,7 @@
         <v>5000</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M16" s="4">
         <v>8000</v>
@@ -2041,10 +2090,10 @@
         <v>30</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="R16" s="17" t="s">
-        <v>140</v>
+        <v>169</v>
+      </c>
+      <c r="R16" s="16" t="s">
+        <v>137</v>
       </c>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
@@ -2052,7 +2101,7 @@
       <c r="X16" s="4"/>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B17" s="4">
+      <c r="B17" s="2">
         <v>13</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -2083,7 +2132,7 @@
         <v>1000</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M17" s="4">
         <v>2000</v>
@@ -2094,10 +2143,10 @@
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="R17" s="17" t="s">
-        <v>141</v>
+        <v>170</v>
+      </c>
+      <c r="R17" s="16" t="s">
+        <v>138</v>
       </c>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
@@ -2105,7 +2154,7 @@
       <c r="X17" s="4"/>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B18" s="4">
+      <c r="B18" s="2">
         <v>14</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -2136,7 +2185,7 @@
         <v>2000</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M18" s="4">
         <v>3000</v>
@@ -2150,8 +2199,8 @@
       <c r="P18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="R18" s="17" t="s">
-        <v>142</v>
+      <c r="R18" s="16" t="s">
+        <v>139</v>
       </c>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
@@ -2159,7 +2208,7 @@
       <c r="X18" s="4"/>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B19" s="4">
+      <c r="B19" s="2">
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -2190,7 +2239,7 @@
         <v>3000</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M19" s="4">
         <v>5000</v>
@@ -2204,8 +2253,8 @@
       <c r="P19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="R19" s="17" t="s">
-        <v>143</v>
+      <c r="R19" s="16" t="s">
+        <v>140</v>
       </c>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
@@ -2213,7 +2262,7 @@
       <c r="X19" s="4"/>
     </row>
     <row r="20" spans="2:24" ht="27" x14ac:dyDescent="0.15">
-      <c r="B20" s="4">
+      <c r="B20" s="2">
         <v>16</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -2244,7 +2293,7 @@
         <v>5000</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M20" s="4">
         <v>8000</v>
@@ -2259,10 +2308,10 @@
         <v>39</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="R20" s="17" t="s">
-        <v>144</v>
+        <v>171</v>
+      </c>
+      <c r="R20" s="16" t="s">
+        <v>141</v>
       </c>
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
@@ -2270,7 +2319,7 @@
       <c r="X20" s="4"/>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B21" s="4">
+      <c r="B21" s="2">
         <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -2301,7 +2350,7 @@
         <v>1000</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M21" s="4">
         <v>2000</v>
@@ -2312,10 +2361,10 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="R21" s="17" t="s">
-        <v>145</v>
+        <v>172</v>
+      </c>
+      <c r="R21" s="16" t="s">
+        <v>142</v>
       </c>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
@@ -2323,14 +2372,14 @@
       <c r="X21" s="4"/>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B22" s="4">
+      <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E22" s="4">
         <v>5</v>
@@ -2354,7 +2403,7 @@
         <v>2000</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M22" s="4">
         <v>3000</v>
@@ -2368,8 +2417,8 @@
       <c r="P22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="R22" s="17" t="s">
-        <v>146</v>
+      <c r="R22" s="16" t="s">
+        <v>143</v>
       </c>
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
@@ -2377,7 +2426,7 @@
       <c r="X22" s="4"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B23" s="4">
+      <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -2408,7 +2457,7 @@
         <v>3000</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M23" s="4">
         <v>5000</v>
@@ -2423,10 +2472,10 @@
         <v>46</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="R23" s="17" t="s">
-        <v>147</v>
+        <v>173</v>
+      </c>
+      <c r="R23" s="16" t="s">
+        <v>144</v>
       </c>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
@@ -2434,7 +2483,7 @@
       <c r="X23" s="4"/>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B24" s="4">
+      <c r="B24" s="2">
         <v>20</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -2465,7 +2514,7 @@
         <v>5000</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M24" s="4">
         <v>8000</v>
@@ -2479,8 +2528,8 @@
       <c r="P24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="R24" s="17" t="s">
-        <v>148</v>
+      <c r="R24" s="16" t="s">
+        <v>145</v>
       </c>
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
@@ -2488,7 +2537,7 @@
       <c r="X24" s="4"/>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B25" s="4">
+      <c r="B25" s="2">
         <v>21</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -2519,7 +2568,7 @@
         <v>1000</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M25" s="4">
         <v>2000</v>
@@ -2530,10 +2579,10 @@
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="R25" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="R25" s="16" t="s">
+        <v>146</v>
       </c>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
@@ -2541,7 +2590,7 @@
       <c r="X25" s="4"/>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B26" s="4">
+      <c r="B26" s="2">
         <v>22</v>
       </c>
       <c r="C26" s="4" t="s">
@@ -2572,7 +2621,7 @@
         <v>2000</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M26" s="4">
         <v>3000</v>
@@ -2586,8 +2635,8 @@
       <c r="P26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="R26" s="17" t="s">
-        <v>151</v>
+      <c r="R26" s="16" t="s">
+        <v>148</v>
       </c>
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
@@ -2595,7 +2644,7 @@
       <c r="X26" s="4"/>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B27" s="4">
+      <c r="B27" s="2">
         <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -2626,7 +2675,7 @@
         <v>3000</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M27" s="4">
         <v>5000</v>
@@ -2640,8 +2689,8 @@
       <c r="P27" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="R27" s="17" t="s">
-        <v>152</v>
+      <c r="R27" s="16" t="s">
+        <v>149</v>
       </c>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
@@ -2649,7 +2698,7 @@
       <c r="X27" s="4"/>
     </row>
     <row r="28" spans="2:24" ht="54" x14ac:dyDescent="0.15">
-      <c r="B28" s="4">
+      <c r="B28" s="2">
         <v>24</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -2680,7 +2729,7 @@
         <v>5000</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M28" s="4">
         <v>8000</v>
@@ -2694,8 +2743,8 @@
       <c r="P28" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="R28" s="17" t="s">
-        <v>153</v>
+      <c r="R28" s="16" t="s">
+        <v>150</v>
       </c>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
@@ -2703,7 +2752,7 @@
       <c r="X28" s="4"/>
     </row>
     <row r="29" spans="2:24" ht="27" x14ac:dyDescent="0.15">
-      <c r="B29" s="4">
+      <c r="B29" s="2">
         <v>25</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -2734,7 +2783,7 @@
         <v>1000</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M29" s="4">
         <v>2000</v>
@@ -2745,7 +2794,7 @@
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
       <c r="R29" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
@@ -2753,7 +2802,7 @@
       <c r="X29" s="4"/>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B30" s="4">
+      <c r="B30" s="2">
         <v>26</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -2784,7 +2833,7 @@
         <v>2000</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M30" s="4">
         <v>3000</v>
@@ -2798,8 +2847,8 @@
       <c r="P30" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="R30" s="17" t="s">
-        <v>155</v>
+      <c r="R30" s="16" t="s">
+        <v>152</v>
       </c>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
@@ -2807,7 +2856,7 @@
       <c r="X30" s="4"/>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B31" s="4">
+      <c r="B31" s="2">
         <v>27</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -2838,7 +2887,7 @@
         <v>3000</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M31" s="4">
         <v>5000</v>
@@ -2853,18 +2902,18 @@
         <v>63</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="R31" s="17" t="s">
-        <v>156</v>
+        <v>124</v>
+      </c>
+      <c r="R31" s="16" t="s">
+        <v>153</v>
       </c>
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
       <c r="X31" s="4"/>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B32" s="4">
+    <row r="32" spans="2:24" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="2">
         <v>28</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2895,7 +2944,7 @@
         <v>5000</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M32" s="4">
         <v>8000</v>
@@ -2910,18 +2959,18 @@
         <v>65</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="R32" s="17" t="s">
-        <v>157</v>
+        <v>174</v>
+      </c>
+      <c r="R32" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
       <c r="X32" s="4"/>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B33" s="4">
+    <row r="33" spans="1:24" ht="54" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="2">
         <v>29</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -2952,7 +3001,7 @@
         <v>1000</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M33" s="4">
         <v>2000</v>
@@ -2962,16 +3011,16 @@
       </c>
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
-      <c r="R33" s="17" t="s">
-        <v>158</v>
+      <c r="R33" s="16" t="s">
+        <v>155</v>
       </c>
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
       <c r="X33" s="4"/>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B34" s="4">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="B34" s="2">
         <v>30</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -3002,7 +3051,7 @@
         <v>2000</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M34" s="4">
         <v>3000</v>
@@ -3016,16 +3065,16 @@
       <c r="P34" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="R34" s="17" t="s">
-        <v>159</v>
+      <c r="R34" s="16" t="s">
+        <v>156</v>
       </c>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
       <c r="X34" s="4"/>
     </row>
-    <row r="35" spans="2:24" ht="27" x14ac:dyDescent="0.15">
-      <c r="B35" s="4">
+    <row r="35" spans="1:24" ht="27" x14ac:dyDescent="0.15">
+      <c r="B35" s="2">
         <v>31</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -3056,7 +3105,7 @@
         <v>3000</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M35" s="4">
         <v>5000</v>
@@ -3070,16 +3119,16 @@
       <c r="P35" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="R35" s="17" t="s">
-        <v>160</v>
+      <c r="R35" s="16" t="s">
+        <v>157</v>
       </c>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
       <c r="X35" s="4"/>
     </row>
-    <row r="36" spans="2:24" ht="27" x14ac:dyDescent="0.15">
-      <c r="B36" s="4">
+    <row r="36" spans="1:24" ht="27" x14ac:dyDescent="0.15">
+      <c r="B36" s="2">
         <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -3110,7 +3159,7 @@
         <v>5000</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M36" s="4">
         <v>8000</v>
@@ -3124,20 +3173,20 @@
       <c r="P36" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="R36" s="17" t="s">
-        <v>161</v>
+      <c r="R36" s="16" t="s">
+        <v>158</v>
       </c>
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
       <c r="X36" s="4"/>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B37" s="4">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="B37" s="2">
         <v>33</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>79</v>
@@ -3164,7 +3213,7 @@
         <v>1000</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M37" s="4">
         <v>2000</v>
@@ -3175,18 +3224,18 @@
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
       <c r="Q37" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="R37" s="17" t="s">
-        <v>162</v>
+        <v>125</v>
+      </c>
+      <c r="R37" s="16" t="s">
+        <v>159</v>
       </c>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
       <c r="X37" s="4"/>
     </row>
-    <row r="38" spans="2:24" ht="27" x14ac:dyDescent="0.15">
-      <c r="B38" s="4">
+    <row r="38" spans="1:24" ht="27" x14ac:dyDescent="0.15">
+      <c r="B38" s="2">
         <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
@@ -3217,7 +3266,7 @@
         <v>2000</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M38" s="4">
         <v>3000</v>
@@ -3231,16 +3280,16 @@
       <c r="P38" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="R38" s="17" t="s">
-        <v>164</v>
+      <c r="R38" s="16" t="s">
+        <v>161</v>
       </c>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
       <c r="X38" s="4"/>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B39" s="4">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="B39" s="2">
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -3271,7 +3320,7 @@
         <v>3000</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M39" s="4">
         <v>5000</v>
@@ -3285,16 +3334,16 @@
       <c r="P39" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="R39" s="17" t="s">
-        <v>165</v>
+      <c r="R39" s="16" t="s">
+        <v>162</v>
       </c>
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
       <c r="X39" s="4"/>
     </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="B40" s="4">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="B40" s="2">
         <v>36</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -3325,7 +3374,7 @@
         <v>5000</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M40" s="4">
         <v>8000</v>
@@ -3339,104 +3388,453 @@
       <c r="P40" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="R40" s="17" t="s">
-        <v>166</v>
+      <c r="R40" s="16" t="s">
+        <v>163</v>
       </c>
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
       <c r="X40" s="4"/>
     </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="R41" s="17"/>
+    <row r="41" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="3"/>
+      <c r="B41" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="4">
+        <v>2</v>
+      </c>
+      <c r="H41" s="4">
+        <v>1</v>
+      </c>
+      <c r="I41" s="4">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4">
+        <v>2000</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M41" s="4">
+        <v>3000</v>
+      </c>
+      <c r="N41" s="4">
+        <v>4</v>
+      </c>
+      <c r="O41" s="4">
+        <v>1</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R41" s="16" t="s">
+        <v>127</v>
+      </c>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
       <c r="X41" s="4"/>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="R42" s="17"/>
+    <row r="42" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="3"/>
+      <c r="B42" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="4">
+        <v>2</v>
+      </c>
+      <c r="H42" s="4">
+        <v>1</v>
+      </c>
+      <c r="I42" s="4">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4">
+        <v>2000</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M42" s="4">
+        <v>3000</v>
+      </c>
+      <c r="N42" s="4">
+        <v>4</v>
+      </c>
+      <c r="O42" s="4">
+        <v>1</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R42" s="16" t="s">
+        <v>127</v>
+      </c>
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
       <c r="X42" s="4"/>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="R43" s="17"/>
+    <row r="43" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="3"/>
+      <c r="B43" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="4">
+        <v>3</v>
+      </c>
+      <c r="H43" s="4">
+        <v>1</v>
+      </c>
+      <c r="I43" s="4">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
+        <v>2000</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M43" s="4">
+        <v>3000</v>
+      </c>
+      <c r="N43" s="4">
+        <v>4</v>
+      </c>
+      <c r="O43" s="4">
+        <v>1</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R43" s="16" t="s">
+        <v>127</v>
+      </c>
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
       <c r="X43" s="4"/>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="R44" s="17"/>
+    <row r="44" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="3"/>
+      <c r="B44" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="4">
+        <v>3</v>
+      </c>
+      <c r="H44" s="4">
+        <v>1</v>
+      </c>
+      <c r="I44" s="4">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4">
+        <v>2000</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M44" s="4">
+        <v>3000</v>
+      </c>
+      <c r="N44" s="4">
+        <v>4</v>
+      </c>
+      <c r="O44" s="4">
+        <v>1</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R44" s="16" t="s">
+        <v>127</v>
+      </c>
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
       <c r="V44" s="4"/>
       <c r="X44" s="4"/>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="R45" s="17"/>
+    <row r="45" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="3"/>
+      <c r="B45" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="4">
+        <v>3</v>
+      </c>
+      <c r="H45" s="4">
+        <v>1</v>
+      </c>
+      <c r="I45" s="4">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4">
+        <v>2000</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M45" s="4">
+        <v>3000</v>
+      </c>
+      <c r="N45" s="4">
+        <v>4</v>
+      </c>
+      <c r="O45" s="4">
+        <v>2</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="16" t="s">
+        <v>127</v>
+      </c>
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
       <c r="X45" s="4"/>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="R46" s="17"/>
+    <row r="46" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="3"/>
+      <c r="B46" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="4">
+        <v>3</v>
+      </c>
+      <c r="H46" s="4">
+        <v>1</v>
+      </c>
+      <c r="I46" s="4">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4">
+        <v>0</v>
+      </c>
+      <c r="K46" s="4">
+        <v>2000</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M46" s="4">
+        <v>3000</v>
+      </c>
+      <c r="N46" s="4">
+        <v>4</v>
+      </c>
+      <c r="O46" s="4">
+        <v>2</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R46" s="16" t="s">
+        <v>127</v>
+      </c>
       <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
       <c r="V46" s="4"/>
       <c r="X46" s="4"/>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.15">
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
+    <row r="47" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="3"/>
+      <c r="B47" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="4">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="4">
+        <v>3</v>
+      </c>
+      <c r="H47" s="4">
+        <v>1</v>
+      </c>
+      <c r="I47" s="4">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4">
+        <v>2000</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M47" s="4">
+        <v>3000</v>
+      </c>
+      <c r="N47" s="4">
+        <v>4</v>
+      </c>
+      <c r="O47" s="4">
+        <v>3</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4"/>
+      <c r="X47" s="4"/>
+    </row>
+    <row r="48" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="3"/>
+      <c r="B48" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="4">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="4">
+        <v>3</v>
+      </c>
+      <c r="H48" s="4">
+        <v>1</v>
+      </c>
+      <c r="I48" s="4">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <v>2000</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M48" s="4">
+        <v>3000</v>
+      </c>
+      <c r="N48" s="4">
+        <v>4</v>
+      </c>
+      <c r="O48" s="4">
+        <v>3</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R48" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4"/>
+      <c r="X48" s="4"/>
     </row>
     <row r="49" spans="4:16" x14ac:dyDescent="0.15">
       <c r="D49" s="4"/>
